--- a/cfg/excel/article_cfg.xlsx
+++ b/cfg/excel/article_cfg.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Emanon\cfg\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Emanon\cfg\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BCBB3E3-FAA4-4E72-821C-B0FD054CD33E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BAAD8B4-7309-4B60-B3DB-BE63D03078FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -43,19 +43,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[TABLE_BEGIN]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>url</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[TABLE_END]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -545,182 +537,168 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="29.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.90625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="29.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.36328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.125" customWidth="1"/>
+    <col min="6" max="6" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.08984375" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="29.375" customWidth="1"/>
-    <col min="12" max="12" width="11.125" customWidth="1"/>
+    <col min="10" max="10" width="29.36328125" customWidth="1"/>
+    <col min="12" max="12" width="11.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A2" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>3</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A4" s="3" t="s">
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A5" s="2">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A6" s="2">
-        <v>2</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A7" s="2">
-        <v>3</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A11" s="2">
-        <v>7</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="1"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A12" s="2" t="s">
-        <v>5</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -732,7 +710,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -743,7 +721,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cfg/excel/article_cfg.xlsx
+++ b/cfg/excel/article_cfg.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -545,9 +545,23 @@
         <v>战令通行证功能</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="str">
+        <v>moon</v>
+      </c>
+      <c r="C11" t="str">
+        <v>secret.png</v>
+      </c>
+      <c r="D11" t="str">
+        <v>to the moon</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/cfg/excel/article_cfg.xlsx
+++ b/cfg/excel/article_cfg.xlsx
@@ -397,11 +397,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D6"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="32.83203125" customWidth="1"/>
+    <col min="2" max="2" width="17.83203125" customWidth="1"/>
+    <col min="3" max="3" width="19.83203125" customWidth="1"/>
     <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -452,13 +452,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="str">
-        <v>gd_occams_razor</v>
+        <v>moon</v>
       </c>
       <c r="C4" t="str">
-        <v>text-markdown.png</v>
+        <v>secret.png</v>
       </c>
       <c r="D4" t="str">
-        <v>如无必要，勿增实体</v>
+        <v>to the moon</v>
       </c>
     </row>
     <row r="5">
@@ -466,13 +466,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="str">
-        <v>gd_system</v>
+        <v>gd_occams_razor</v>
       </c>
       <c r="C5" t="str">
         <v>text-markdown.png</v>
       </c>
       <c r="D5" t="str">
-        <v>复杂游戏系统设计与"涌现"理论</v>
+        <v>如无必要，勿增实体</v>
       </c>
     </row>
     <row r="6">
@@ -480,88 +480,18 @@
         <v>3</v>
       </c>
       <c r="B6" t="str">
-        <v>gd_sample_hero_ape</v>
+        <v>gd_system</v>
       </c>
       <c r="C6" t="str">
-        <v>application-x-genesis-rom.png</v>
+        <v>text-markdown.png</v>
       </c>
       <c r="D6" t="str">
-        <v>角色设计：无聊猿</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>4</v>
-      </c>
-      <c r="B7" t="str">
-        <v>gd_sample_ingame_capture</v>
-      </c>
-      <c r="C7" t="str">
-        <v>application-x-nes-rom.png</v>
-      </c>
-      <c r="D7" t="str">
-        <v>占领模式战场规则</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>5</v>
-      </c>
-      <c r="B8" t="str">
-        <v>gd_sample_ingame_recoil</v>
-      </c>
-      <c r="C8" t="str">
-        <v>application-x-nes-rom.png</v>
-      </c>
-      <c r="D8" t="str">
-        <v>枪械后坐力规则</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>6</v>
-      </c>
-      <c r="B9" t="str">
-        <v>gd_sample_ingame_party_point</v>
-      </c>
-      <c r="C9" t="str">
-        <v>application-x-gamecube-rom.png</v>
-      </c>
-      <c r="D9" t="str">
-        <v>局内派对点奖励规则</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>7</v>
-      </c>
-      <c r="B10" t="str">
-        <v>gd_sample_system_battlepass</v>
-      </c>
-      <c r="C10" t="str">
-        <v>application-x-gamecube-rom.png</v>
-      </c>
-      <c r="D10" t="str">
-        <v>战令通行证功能</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>8</v>
-      </c>
-      <c r="B11" t="str">
-        <v>moon</v>
-      </c>
-      <c r="C11" t="str">
-        <v>secret.png</v>
-      </c>
-      <c r="D11" t="str">
-        <v>to the moon</v>
+        <v>复杂游戏系统设计与"涌现"理论</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>